--- a/backend/data/financials_by_company/10N.F.xlsx
+++ b/backend/data/financials_by_company/10N.F.xlsx
@@ -672,58 +672,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-3449380</v>
+        <v>-6233730</v>
       </c>
       <c r="C2" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="D2" t="n">
-        <v>506741000</v>
+        <v>169762000</v>
       </c>
       <c r="E2" t="n">
-        <v>-15679000</v>
+        <v>-36669000</v>
       </c>
       <c r="F2" t="n">
-        <v>-15679000</v>
+        <v>-36669000</v>
       </c>
       <c r="G2" t="n">
-        <v>65566000</v>
+        <v>-117117000</v>
       </c>
       <c r="H2" t="n">
-        <v>323906000</v>
+        <v>222885000</v>
       </c>
       <c r="I2" t="n">
-        <v>2606817000</v>
+        <v>1068161000</v>
       </c>
       <c r="J2" t="n">
-        <v>491062000</v>
+        <v>133093000</v>
       </c>
       <c r="K2" t="n">
-        <v>167156000</v>
+        <v>-89792000</v>
       </c>
       <c r="L2" t="n">
-        <v>-91803000</v>
+        <v>-51459000</v>
       </c>
       <c r="M2" t="n">
-        <v>90537000</v>
+        <v>51280000</v>
       </c>
       <c r="N2" t="n">
-        <v>432000</v>
+        <v>859000</v>
       </c>
       <c r="O2" t="n">
-        <v>77795620</v>
+        <v>-86681730</v>
       </c>
       <c r="P2" t="n">
-        <v>65566000</v>
+        <v>-117117000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2672438000</v>
+        <v>1097690000</v>
       </c>
       <c r="R2" t="n">
-        <v>260737000</v>
+        <v>-14663000</v>
       </c>
       <c r="S2" t="n">
         <v>17543750</v>
@@ -732,148 +732,150 @@
         <v>17543750</v>
       </c>
       <c r="U2" t="n">
-        <v>3.74</v>
+        <v>-6.68</v>
       </c>
       <c r="V2" t="n">
-        <v>3.74</v>
+        <v>-6.68</v>
       </c>
       <c r="W2" t="n">
-        <v>65566000</v>
+        <v>-117117000</v>
       </c>
       <c r="X2" t="n">
-        <v>65566000</v>
+        <v>-117117000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>65566000</v>
+        <v>-117117000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-83000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>65649000</v>
+        <v>-117117000</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>65649000</v>
+        <v>-117117000</v>
       </c>
       <c r="AE2" t="n">
-        <v>10970000</v>
+        <v>-23955000</v>
       </c>
       <c r="AF2" t="n">
-        <v>76619000</v>
+        <v>-141072000</v>
       </c>
       <c r="AG2" t="n">
-        <v>8761000</v>
+        <v>-36669000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-10609000</v>
+        <v>-80000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1848000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>162000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>36587000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>-91803000</v>
+        <v>-51459000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1698000</v>
+        <v>1038000</v>
       </c>
       <c r="AM2" t="n">
-        <v>90537000</v>
+        <v>51280000</v>
       </c>
       <c r="AN2" t="n">
-        <v>432000</v>
+        <v>859000</v>
       </c>
       <c r="AO2" t="n">
-        <v>253859000</v>
+        <v>22606000</v>
       </c>
       <c r="AP2" t="n">
-        <v>65621000</v>
+        <v>29529000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1299000</v>
+        <v>2914000</v>
       </c>
       <c r="AR2" t="n">
-        <v>69302000</v>
+        <v>36171000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2058000</v>
+        <v>599000</v>
       </c>
       <c r="AT2" t="n">
-        <v>67244000</v>
+        <v>35572000</v>
       </c>
       <c r="AU2" t="n">
-        <v>319480000</v>
+        <v>52135000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2606817000</v>
+        <v>1068161000</v>
       </c>
       <c r="AW2" t="n">
-        <v>2926297000</v>
+        <v>1120296000</v>
       </c>
       <c r="AX2" t="n">
-        <v>2926297000</v>
+        <v>1120296000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>3156567</v>
+        <v>3502800</v>
       </c>
       <c r="C3" t="n">
-        <v>0.183</v>
+        <v>0.063</v>
       </c>
       <c r="D3" t="n">
-        <v>528146000</v>
+        <v>287354000</v>
       </c>
       <c r="E3" t="n">
-        <v>17249000</v>
+        <v>55600000</v>
       </c>
       <c r="F3" t="n">
-        <v>17249000</v>
+        <v>55600000</v>
       </c>
       <c r="G3" t="n">
-        <v>196435000</v>
+        <v>72271000</v>
       </c>
       <c r="H3" t="n">
-        <v>238991000</v>
+        <v>217063000</v>
       </c>
       <c r="I3" t="n">
-        <v>2404322000</v>
+        <v>2039717000</v>
       </c>
       <c r="J3" t="n">
-        <v>545395000</v>
+        <v>342954000</v>
       </c>
       <c r="K3" t="n">
-        <v>306404000</v>
+        <v>125891000</v>
       </c>
       <c r="L3" t="n">
-        <v>-74473000</v>
+        <v>-61356000</v>
       </c>
       <c r="M3" t="n">
-        <v>65873000</v>
+        <v>48753000</v>
       </c>
       <c r="N3" t="n">
-        <v>2393000</v>
+        <v>1079000</v>
       </c>
       <c r="O3" t="n">
-        <v>182342567</v>
+        <v>20173800</v>
       </c>
       <c r="P3" t="n">
-        <v>196435000</v>
+        <v>72271000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2461842000</v>
+        <v>2083751000</v>
       </c>
       <c r="R3" t="n">
-        <v>166159000</v>
+        <v>225616000</v>
       </c>
       <c r="S3" t="n">
         <v>17543750</v>
@@ -882,146 +884,150 @@
         <v>17543750</v>
       </c>
       <c r="U3" t="n">
-        <v>11.2</v>
+        <v>4.12</v>
       </c>
       <c r="V3" t="n">
-        <v>11.2</v>
+        <v>4.12</v>
       </c>
       <c r="W3" t="n">
-        <v>196435000</v>
+        <v>72271000</v>
       </c>
       <c r="X3" t="n">
-        <v>196435000</v>
+        <v>72271000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>196435000</v>
+        <v>72271000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>196435000</v>
+        <v>72271000</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>196435000</v>
+        <v>72271000</v>
       </c>
       <c r="AE3" t="n">
-        <v>44096000</v>
+        <v>4867000</v>
       </c>
       <c r="AF3" t="n">
-        <v>240531000</v>
+        <v>77138000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-197000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>52337000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-52589000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>197000</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>252000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
       <c r="AK3" t="n">
-        <v>-74473000</v>
+        <v>-61356000</v>
       </c>
       <c r="AL3" t="n">
-        <v>10993000</v>
+        <v>13682000</v>
       </c>
       <c r="AM3" t="n">
-        <v>65873000</v>
+        <v>48753000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2393000</v>
+        <v>1079000</v>
       </c>
       <c r="AO3" t="n">
-        <v>164101000</v>
+        <v>172047000</v>
       </c>
       <c r="AP3" t="n">
-        <v>57520000</v>
+        <v>44034000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2131000</v>
+        <v>1424000</v>
       </c>
       <c r="AR3" t="n">
-        <v>57581000</v>
+        <v>43386000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1270000</v>
+        <v>1061000</v>
       </c>
       <c r="AT3" t="n">
-        <v>56311000</v>
+        <v>42325000</v>
       </c>
       <c r="AU3" t="n">
-        <v>221621000</v>
+        <v>216081000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2404322000</v>
+        <v>2039717000</v>
       </c>
       <c r="AW3" t="n">
-        <v>2625943000</v>
+        <v>2255798000</v>
       </c>
       <c r="AX3" t="n">
-        <v>2625943000</v>
+        <v>2255798000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3502800</v>
+        <v>3156567</v>
       </c>
       <c r="C4" t="n">
-        <v>0.063</v>
+        <v>0.183</v>
       </c>
       <c r="D4" t="n">
-        <v>287354000</v>
+        <v>528146000</v>
       </c>
       <c r="E4" t="n">
-        <v>55600000</v>
+        <v>17249000</v>
       </c>
       <c r="F4" t="n">
-        <v>55600000</v>
+        <v>17249000</v>
       </c>
       <c r="G4" t="n">
-        <v>72271000</v>
+        <v>196435000</v>
       </c>
       <c r="H4" t="n">
-        <v>217063000</v>
+        <v>238991000</v>
       </c>
       <c r="I4" t="n">
-        <v>2039717000</v>
+        <v>2404322000</v>
       </c>
       <c r="J4" t="n">
-        <v>342954000</v>
+        <v>545395000</v>
       </c>
       <c r="K4" t="n">
-        <v>125891000</v>
+        <v>306404000</v>
       </c>
       <c r="L4" t="n">
-        <v>-61356000</v>
+        <v>-74473000</v>
       </c>
       <c r="M4" t="n">
-        <v>48753000</v>
+        <v>65873000</v>
       </c>
       <c r="N4" t="n">
-        <v>1079000</v>
+        <v>2393000</v>
       </c>
       <c r="O4" t="n">
-        <v>20173800</v>
+        <v>182342567</v>
       </c>
       <c r="P4" t="n">
-        <v>72271000</v>
+        <v>196435000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2083751000</v>
+        <v>2461842000</v>
       </c>
       <c r="R4" t="n">
-        <v>225616000</v>
+        <v>166159000</v>
       </c>
       <c r="S4" t="n">
         <v>17543750</v>
@@ -1030,150 +1036,146 @@
         <v>17543750</v>
       </c>
       <c r="U4" t="n">
-        <v>4.12</v>
+        <v>11.2</v>
       </c>
       <c r="V4" t="n">
-        <v>4.12</v>
+        <v>11.2</v>
       </c>
       <c r="W4" t="n">
-        <v>72271000</v>
+        <v>196435000</v>
       </c>
       <c r="X4" t="n">
-        <v>72271000</v>
+        <v>196435000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>72271000</v>
+        <v>196435000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>72271000</v>
+        <v>196435000</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>72271000</v>
+        <v>196435000</v>
       </c>
       <c r="AE4" t="n">
-        <v>4867000</v>
+        <v>44096000</v>
       </c>
       <c r="AF4" t="n">
-        <v>77138000</v>
+        <v>240531000</v>
       </c>
       <c r="AG4" t="n">
-        <v>52337000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-52589000</v>
-      </c>
+        <v>-197000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>252000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+        <v>197000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>-61356000</v>
+        <v>-74473000</v>
       </c>
       <c r="AL4" t="n">
-        <v>13682000</v>
+        <v>10993000</v>
       </c>
       <c r="AM4" t="n">
-        <v>48753000</v>
+        <v>65873000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1079000</v>
+        <v>2393000</v>
       </c>
       <c r="AO4" t="n">
-        <v>172047000</v>
+        <v>164101000</v>
       </c>
       <c r="AP4" t="n">
-        <v>44034000</v>
+        <v>57520000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1424000</v>
+        <v>2131000</v>
       </c>
       <c r="AR4" t="n">
-        <v>43386000</v>
+        <v>57581000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1061000</v>
+        <v>1270000</v>
       </c>
       <c r="AT4" t="n">
-        <v>42325000</v>
+        <v>56311000</v>
       </c>
       <c r="AU4" t="n">
-        <v>216081000</v>
+        <v>221621000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2039717000</v>
+        <v>2404322000</v>
       </c>
       <c r="AW4" t="n">
-        <v>2255798000</v>
+        <v>2625943000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2255798000</v>
+        <v>2625943000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-6233730</v>
+        <v>-3449380</v>
       </c>
       <c r="C5" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="D5" t="n">
-        <v>169762000</v>
+        <v>506741000</v>
       </c>
       <c r="E5" t="n">
-        <v>-36669000</v>
+        <v>-15679000</v>
       </c>
       <c r="F5" t="n">
-        <v>-36669000</v>
+        <v>-15679000</v>
       </c>
       <c r="G5" t="n">
-        <v>-117117000</v>
+        <v>65566000</v>
       </c>
       <c r="H5" t="n">
-        <v>222885000</v>
+        <v>323906000</v>
       </c>
       <c r="I5" t="n">
-        <v>1068161000</v>
+        <v>2606817000</v>
       </c>
       <c r="J5" t="n">
-        <v>133093000</v>
+        <v>491062000</v>
       </c>
       <c r="K5" t="n">
-        <v>-89792000</v>
+        <v>167156000</v>
       </c>
       <c r="L5" t="n">
-        <v>-51459000</v>
+        <v>-91803000</v>
       </c>
       <c r="M5" t="n">
-        <v>51280000</v>
+        <v>90537000</v>
       </c>
       <c r="N5" t="n">
-        <v>859000</v>
+        <v>432000</v>
       </c>
       <c r="O5" t="n">
-        <v>-86681730</v>
+        <v>77795620</v>
       </c>
       <c r="P5" t="n">
-        <v>-117117000</v>
+        <v>65566000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1097690000</v>
+        <v>2672438000</v>
       </c>
       <c r="R5" t="n">
-        <v>-14663000</v>
+        <v>260737000</v>
       </c>
       <c r="S5" t="n">
         <v>17543750</v>
@@ -1182,94 +1184,92 @@
         <v>17543750</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.68</v>
+        <v>3.74</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.68</v>
+        <v>3.74</v>
       </c>
       <c r="W5" t="n">
-        <v>-117117000</v>
+        <v>65566000</v>
       </c>
       <c r="X5" t="n">
-        <v>-117117000</v>
+        <v>65566000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-117117000</v>
+        <v>65566000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-83000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-117117000</v>
+        <v>65649000</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-117117000</v>
+        <v>65649000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-23955000</v>
+        <v>10970000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-141072000</v>
+        <v>76619000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-36669000</v>
+        <v>8761000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-80000</v>
+        <v>-10609000</v>
       </c>
       <c r="AI5" t="n">
-        <v>162000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>36587000</v>
-      </c>
+        <v>1848000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>-51459000</v>
+        <v>-91803000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1038000</v>
+        <v>1698000</v>
       </c>
       <c r="AM5" t="n">
-        <v>51280000</v>
+        <v>90537000</v>
       </c>
       <c r="AN5" t="n">
-        <v>859000</v>
+        <v>432000</v>
       </c>
       <c r="AO5" t="n">
-        <v>22606000</v>
+        <v>253859000</v>
       </c>
       <c r="AP5" t="n">
-        <v>29529000</v>
+        <v>65621000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2914000</v>
+        <v>-1299000</v>
       </c>
       <c r="AR5" t="n">
-        <v>36171000</v>
+        <v>69302000</v>
       </c>
       <c r="AS5" t="n">
-        <v>599000</v>
+        <v>2058000</v>
       </c>
       <c r="AT5" t="n">
-        <v>35572000</v>
+        <v>67244000</v>
       </c>
       <c r="AU5" t="n">
-        <v>52135000</v>
+        <v>319480000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1068161000</v>
+        <v>2606817000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1120296000</v>
+        <v>2926297000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1120296000</v>
+        <v>2926297000</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>17543750</v>
@@ -1633,42 +1633,44 @@
       <c r="C2" t="n">
         <v>17543750</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>43890000</v>
+      </c>
       <c r="E2" t="n">
-        <v>2076371000</v>
+        <v>1463646000</v>
       </c>
       <c r="F2" t="n">
-        <v>335833000</v>
+        <v>88781000</v>
       </c>
       <c r="G2" t="n">
-        <v>530147000</v>
+        <v>401626000</v>
       </c>
       <c r="H2" t="n">
-        <v>-230067000</v>
+        <v>-205099000</v>
       </c>
       <c r="I2" t="n">
-        <v>335833000</v>
+        <v>88781000</v>
       </c>
       <c r="J2" t="n">
-        <v>1892341000</v>
+        <v>1151068000</v>
       </c>
       <c r="K2" t="n">
-        <v>346117000</v>
+        <v>89048000</v>
       </c>
       <c r="L2" t="n">
-        <v>363158000</v>
+        <v>286148000</v>
       </c>
       <c r="M2" t="n">
-        <v>346671000</v>
+        <v>89048000</v>
       </c>
       <c r="N2" t="n">
-        <v>554000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>346117000</v>
+        <v>89048000</v>
       </c>
       <c r="P2" t="n">
-        <v>210602000</v>
+        <v>-46478000</v>
       </c>
       <c r="Q2" t="n">
         <v>117983000</v>
@@ -1680,154 +1682,150 @@
         <v>17544000</v>
       </c>
       <c r="T2" t="n">
-        <v>2361953000</v>
+        <v>1657951000</v>
       </c>
       <c r="U2" t="n">
-        <v>1642509000</v>
+        <v>1101229000</v>
       </c>
       <c r="V2" t="n">
-        <v>35639000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>6580000</v>
-      </c>
+        <v>23697000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>1600290000</v>
+        <v>1077532000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1583249000</v>
+        <v>880432000</v>
       </c>
       <c r="Z2" t="n">
-        <v>17041000</v>
+        <v>197100000</v>
       </c>
       <c r="AA2" t="n">
-        <v>719444000</v>
+        <v>556722000</v>
       </c>
       <c r="AB2" t="n">
-        <v>241000</v>
+        <v>146000</v>
       </c>
       <c r="AC2" t="n">
-        <v>476081000</v>
+        <v>386114000</v>
       </c>
       <c r="AD2" t="n">
-        <v>309092000</v>
+        <v>270636000</v>
       </c>
       <c r="AE2" t="n">
-        <v>166989000</v>
+        <v>115478000</v>
       </c>
       <c r="AF2" t="n">
-        <v>6382000</v>
+        <v>1922000</v>
       </c>
       <c r="AG2" t="n">
-        <v>136869000</v>
+        <v>119610000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2329000</v>
+        <v>11042000</v>
       </c>
       <c r="AI2" t="n">
-        <v>19159000</v>
+        <v>2395000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>115381000</v>
+        <v>106173000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2708624000</v>
+        <v>1746999000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2219247000</v>
+        <v>1395376000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>29622000</v>
       </c>
       <c r="AN2" t="n">
-        <v>66876000</v>
+        <v>43016000</v>
       </c>
       <c r="AO2" t="n">
-        <v>66876000</v>
+        <v>43016000</v>
       </c>
       <c r="AP2" t="n">
-        <v>10284000</v>
+        <v>267000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10284000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
+        <v>267000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>2030863000</v>
+        <v>1236258000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1133786000</v>
+        <v>-655182000</v>
       </c>
       <c r="AU2" t="n">
-        <v>3164649000</v>
+        <v>1891440000</v>
       </c>
       <c r="AV2" t="n">
-        <v>30548000</v>
+        <v>7160000</v>
       </c>
       <c r="AW2" t="n">
-        <v>4031000</v>
+        <v>1490000</v>
       </c>
       <c r="AX2" t="n">
-        <v>3107618000</v>
+        <v>1871172000</v>
       </c>
       <c r="AY2" t="n">
-        <v>22452000</v>
+        <v>11618000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>489377000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2064000</v>
-      </c>
+        <v>351623000</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>15838000</v>
+        <v>8190000</v>
       </c>
       <c r="BD2" t="n">
-        <v>9499000</v>
+        <v>4396000</v>
       </c>
       <c r="BE2" t="n">
-        <v>10584000</v>
+        <v>4223000</v>
       </c>
       <c r="BF2" t="n">
-        <v>10584000</v>
+        <v>4223000</v>
       </c>
       <c r="BG2" t="n">
-        <v>6993000</v>
+        <v>4257000</v>
       </c>
       <c r="BH2" t="n">
-        <v>19143000</v>
+        <v>6164000</v>
       </c>
       <c r="BI2" t="n">
-        <v>125755000</v>
+        <v>55705000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-3493000</v>
+        <v>-1889000</v>
       </c>
       <c r="BK2" t="n">
-        <v>129248000</v>
+        <v>57594000</v>
       </c>
       <c r="BL2" t="n">
-        <v>299501000</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
+        <v>268688000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>45000</v>
+      </c>
       <c r="BN2" t="n">
-        <v>299501000</v>
+        <v>268688000</v>
       </c>
       <c r="BO2" t="n">
-        <v>151752000</v>
+        <v>18301000</v>
       </c>
       <c r="BP2" t="n">
-        <v>147749000</v>
+        <v>250387000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>17543750</v>
@@ -1837,40 +1835,40 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>1537841000</v>
+        <v>1462832000</v>
       </c>
       <c r="F3" t="n">
-        <v>353336000</v>
+        <v>161063000</v>
       </c>
       <c r="G3" t="n">
-        <v>547091000</v>
+        <v>377024000</v>
       </c>
       <c r="H3" t="n">
-        <v>-200834000</v>
+        <v>-149057000</v>
       </c>
       <c r="I3" t="n">
-        <v>353336000</v>
+        <v>161063000</v>
       </c>
       <c r="J3" t="n">
-        <v>1348504000</v>
+        <v>1247127000</v>
       </c>
       <c r="K3" t="n">
-        <v>357754000</v>
+        <v>161319000</v>
       </c>
       <c r="L3" t="n">
-        <v>357754000</v>
+        <v>255479000</v>
       </c>
       <c r="M3" t="n">
-        <v>357754000</v>
+        <v>161319000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>357754000</v>
+        <v>161319000</v>
       </c>
       <c r="P3" t="n">
-        <v>222228000</v>
+        <v>25793000</v>
       </c>
       <c r="Q3" t="n">
         <v>117983000</v>
@@ -1882,105 +1880,103 @@
         <v>17544000</v>
       </c>
       <c r="T3" t="n">
-        <v>1779116000</v>
+        <v>1688483000</v>
       </c>
       <c r="U3" t="n">
-        <v>1125356000</v>
+        <v>1116534000</v>
       </c>
       <c r="V3" t="n">
-        <v>26966000</v>
+        <v>26393000</v>
       </c>
       <c r="W3" t="n">
-        <v>10052000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1088338000</v>
+        <v>1090141000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1088338000</v>
+        <v>995981000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>94160000</v>
       </c>
       <c r="AA3" t="n">
-        <v>653760000</v>
+        <v>571949000</v>
       </c>
       <c r="AB3" t="n">
-        <v>193000</v>
+        <v>133000</v>
       </c>
       <c r="AC3" t="n">
-        <v>449503000</v>
+        <v>372691000</v>
       </c>
       <c r="AD3" t="n">
-        <v>260166000</v>
+        <v>251146000</v>
       </c>
       <c r="AE3" t="n">
-        <v>189337000</v>
+        <v>121545000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2817000</v>
+        <v>2176000</v>
       </c>
       <c r="AG3" t="n">
-        <v>122136000</v>
+        <v>128502000</v>
       </c>
       <c r="AH3" t="n">
-        <v>10325000</v>
+        <v>11042000</v>
       </c>
       <c r="AI3" t="n">
-        <v>5084000</v>
+        <v>3789000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>106727000</v>
+        <v>113671000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2136870000</v>
+        <v>1849802000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1683944000</v>
+        <v>1426910000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>24861000</v>
       </c>
       <c r="AN3" t="n">
-        <v>54497000</v>
+        <v>47574000</v>
       </c>
       <c r="AO3" t="n">
-        <v>54497000</v>
+        <v>47574000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4418000</v>
+        <v>256000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4418000</v>
+        <v>256000</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>1526393000</v>
+        <v>1258804000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1022196000</v>
+        <v>-784198000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2548589000</v>
+        <v>2043002000</v>
       </c>
       <c r="AV3" t="n">
-        <v>6611000</v>
+        <v>7330000</v>
       </c>
       <c r="AW3" t="n">
-        <v>2310000</v>
+        <v>1697000</v>
       </c>
       <c r="AX3" t="n">
-        <v>2526460000</v>
+        <v>2020827000</v>
       </c>
       <c r="AY3" t="n">
-        <v>13208000</v>
+        <v>13148000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>452926000</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
+        <v>422892000</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
@@ -1988,46 +1984,46 @@
         <v>7623000</v>
       </c>
       <c r="BD3" t="n">
-        <v>5305000</v>
+        <v>6951000</v>
       </c>
       <c r="BE3" t="n">
-        <v>6788000</v>
+        <v>4558000</v>
       </c>
       <c r="BF3" t="n">
-        <v>6788000</v>
+        <v>4558000</v>
       </c>
       <c r="BG3" t="n">
-        <v>12537000</v>
+        <v>4114000</v>
       </c>
       <c r="BH3" t="n">
-        <v>19494000</v>
+        <v>6778000</v>
       </c>
       <c r="BI3" t="n">
-        <v>125512000</v>
+        <v>99541000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-5376000</v>
+        <v>-3121000</v>
       </c>
       <c r="BK3" t="n">
-        <v>130888000</v>
+        <v>102662000</v>
       </c>
       <c r="BL3" t="n">
-        <v>275667000</v>
+        <v>293327000</v>
       </c>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>275667000</v>
+        <v>293327000</v>
       </c>
       <c r="BO3" t="n">
-        <v>102125000</v>
+        <v>59267000</v>
       </c>
       <c r="BP3" t="n">
-        <v>173542000</v>
+        <v>234060000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>17543750</v>
@@ -2037,40 +2033,40 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>1462832000</v>
+        <v>1537841000</v>
       </c>
       <c r="F4" t="n">
-        <v>161063000</v>
+        <v>353336000</v>
       </c>
       <c r="G4" t="n">
-        <v>377024000</v>
+        <v>547091000</v>
       </c>
       <c r="H4" t="n">
-        <v>-149057000</v>
+        <v>-200834000</v>
       </c>
       <c r="I4" t="n">
-        <v>161063000</v>
+        <v>353336000</v>
       </c>
       <c r="J4" t="n">
-        <v>1247127000</v>
+        <v>1348504000</v>
       </c>
       <c r="K4" t="n">
-        <v>161319000</v>
+        <v>357754000</v>
       </c>
       <c r="L4" t="n">
-        <v>255479000</v>
+        <v>357754000</v>
       </c>
       <c r="M4" t="n">
-        <v>161319000</v>
+        <v>357754000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>161319000</v>
+        <v>357754000</v>
       </c>
       <c r="P4" t="n">
-        <v>25793000</v>
+        <v>222228000</v>
       </c>
       <c r="Q4" t="n">
         <v>117983000</v>
@@ -2082,103 +2078,105 @@
         <v>17544000</v>
       </c>
       <c r="T4" t="n">
-        <v>1688483000</v>
+        <v>1779116000</v>
       </c>
       <c r="U4" t="n">
-        <v>1116534000</v>
+        <v>1125356000</v>
       </c>
       <c r="V4" t="n">
-        <v>26393000</v>
+        <v>26966000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>10052000</v>
       </c>
       <c r="X4" t="n">
-        <v>1090141000</v>
+        <v>1088338000</v>
       </c>
       <c r="Y4" t="n">
-        <v>995981000</v>
+        <v>1088338000</v>
       </c>
       <c r="Z4" t="n">
-        <v>94160000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>571949000</v>
+        <v>653760000</v>
       </c>
       <c r="AB4" t="n">
-        <v>133000</v>
+        <v>193000</v>
       </c>
       <c r="AC4" t="n">
-        <v>372691000</v>
+        <v>449503000</v>
       </c>
       <c r="AD4" t="n">
-        <v>251146000</v>
+        <v>260166000</v>
       </c>
       <c r="AE4" t="n">
-        <v>121545000</v>
+        <v>189337000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2176000</v>
+        <v>2817000</v>
       </c>
       <c r="AG4" t="n">
-        <v>128502000</v>
+        <v>122136000</v>
       </c>
       <c r="AH4" t="n">
-        <v>11042000</v>
+        <v>10325000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3789000</v>
+        <v>5084000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>113671000</v>
+        <v>106727000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1849802000</v>
+        <v>2136870000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1426910000</v>
+        <v>1683944000</v>
       </c>
       <c r="AM4" t="n">
-        <v>24861000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>47574000</v>
+        <v>54497000</v>
       </c>
       <c r="AO4" t="n">
-        <v>47574000</v>
+        <v>54497000</v>
       </c>
       <c r="AP4" t="n">
-        <v>256000</v>
+        <v>4418000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>256000</v>
+        <v>4418000</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>1258804000</v>
+        <v>1526393000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-784198000</v>
+        <v>-1022196000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2043002000</v>
+        <v>2548589000</v>
       </c>
       <c r="AV4" t="n">
-        <v>7330000</v>
+        <v>6611000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1697000</v>
+        <v>2310000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2020827000</v>
+        <v>2526460000</v>
       </c>
       <c r="AY4" t="n">
-        <v>13148000</v>
+        <v>13208000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>422892000</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
+        <v>452926000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
@@ -2186,46 +2184,46 @@
         <v>7623000</v>
       </c>
       <c r="BD4" t="n">
-        <v>6951000</v>
+        <v>5305000</v>
       </c>
       <c r="BE4" t="n">
-        <v>4558000</v>
+        <v>6788000</v>
       </c>
       <c r="BF4" t="n">
-        <v>4558000</v>
+        <v>6788000</v>
       </c>
       <c r="BG4" t="n">
-        <v>4114000</v>
+        <v>12537000</v>
       </c>
       <c r="BH4" t="n">
-        <v>6778000</v>
+        <v>19494000</v>
       </c>
       <c r="BI4" t="n">
-        <v>99541000</v>
+        <v>125512000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-3121000</v>
+        <v>-5376000</v>
       </c>
       <c r="BK4" t="n">
-        <v>102662000</v>
+        <v>130888000</v>
       </c>
       <c r="BL4" t="n">
-        <v>293327000</v>
+        <v>275667000</v>
       </c>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>293327000</v>
+        <v>275667000</v>
       </c>
       <c r="BO4" t="n">
-        <v>59267000</v>
+        <v>102125000</v>
       </c>
       <c r="BP4" t="n">
-        <v>234060000</v>
+        <v>173542000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>17543750</v>
@@ -2233,44 +2231,42 @@
       <c r="C5" t="n">
         <v>17543750</v>
       </c>
-      <c r="D5" t="n">
-        <v>43890000</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>1463646000</v>
+        <v>2076371000</v>
       </c>
       <c r="F5" t="n">
-        <v>88781000</v>
+        <v>335833000</v>
       </c>
       <c r="G5" t="n">
-        <v>401626000</v>
+        <v>530147000</v>
       </c>
       <c r="H5" t="n">
-        <v>-205099000</v>
+        <v>-230067000</v>
       </c>
       <c r="I5" t="n">
-        <v>88781000</v>
+        <v>335833000</v>
       </c>
       <c r="J5" t="n">
-        <v>1151068000</v>
+        <v>1892341000</v>
       </c>
       <c r="K5" t="n">
-        <v>89048000</v>
+        <v>346117000</v>
       </c>
       <c r="L5" t="n">
-        <v>286148000</v>
+        <v>363158000</v>
       </c>
       <c r="M5" t="n">
-        <v>89048000</v>
+        <v>346671000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>554000</v>
       </c>
       <c r="O5" t="n">
-        <v>89048000</v>
+        <v>346117000</v>
       </c>
       <c r="P5" t="n">
-        <v>-46478000</v>
+        <v>210602000</v>
       </c>
       <c r="Q5" t="n">
         <v>117983000</v>
@@ -2282,145 +2278,149 @@
         <v>17544000</v>
       </c>
       <c r="T5" t="n">
-        <v>1657951000</v>
+        <v>2361953000</v>
       </c>
       <c r="U5" t="n">
-        <v>1101229000</v>
+        <v>1642509000</v>
       </c>
       <c r="V5" t="n">
-        <v>23697000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>35639000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6580000</v>
+      </c>
       <c r="X5" t="n">
-        <v>1077532000</v>
+        <v>1600290000</v>
       </c>
       <c r="Y5" t="n">
-        <v>880432000</v>
+        <v>1583249000</v>
       </c>
       <c r="Z5" t="n">
-        <v>197100000</v>
+        <v>17041000</v>
       </c>
       <c r="AA5" t="n">
-        <v>556722000</v>
+        <v>719444000</v>
       </c>
       <c r="AB5" t="n">
-        <v>146000</v>
+        <v>241000</v>
       </c>
       <c r="AC5" t="n">
-        <v>386114000</v>
+        <v>476081000</v>
       </c>
       <c r="AD5" t="n">
-        <v>270636000</v>
+        <v>309092000</v>
       </c>
       <c r="AE5" t="n">
-        <v>115478000</v>
+        <v>166989000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1922000</v>
+        <v>6382000</v>
       </c>
       <c r="AG5" t="n">
-        <v>119610000</v>
+        <v>136869000</v>
       </c>
       <c r="AH5" t="n">
-        <v>11042000</v>
+        <v>2329000</v>
       </c>
       <c r="AI5" t="n">
-        <v>2395000</v>
+        <v>19159000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>106173000</v>
+        <v>115381000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1746999000</v>
+        <v>2708624000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1395376000</v>
+        <v>2219247000</v>
       </c>
       <c r="AM5" t="n">
-        <v>29622000</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>43016000</v>
+        <v>66876000</v>
       </c>
       <c r="AO5" t="n">
-        <v>43016000</v>
+        <v>66876000</v>
       </c>
       <c r="AP5" t="n">
-        <v>267000</v>
+        <v>10284000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>267000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>10284000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
       <c r="AS5" t="n">
-        <v>1236258000</v>
+        <v>2030863000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-655182000</v>
+        <v>-1133786000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1891440000</v>
+        <v>3164649000</v>
       </c>
       <c r="AV5" t="n">
-        <v>7160000</v>
+        <v>30548000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1490000</v>
+        <v>4031000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1871172000</v>
+        <v>3107618000</v>
       </c>
       <c r="AY5" t="n">
-        <v>11618000</v>
+        <v>22452000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>351623000</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
+        <v>489377000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2064000</v>
+      </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>8190000</v>
+        <v>15838000</v>
       </c>
       <c r="BD5" t="n">
-        <v>4396000</v>
+        <v>9499000</v>
       </c>
       <c r="BE5" t="n">
-        <v>4223000</v>
+        <v>10584000</v>
       </c>
       <c r="BF5" t="n">
-        <v>4223000</v>
+        <v>10584000</v>
       </c>
       <c r="BG5" t="n">
-        <v>4257000</v>
+        <v>6993000</v>
       </c>
       <c r="BH5" t="n">
-        <v>6164000</v>
+        <v>19143000</v>
       </c>
       <c r="BI5" t="n">
-        <v>55705000</v>
+        <v>125755000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-1889000</v>
+        <v>-3493000</v>
       </c>
       <c r="BK5" t="n">
-        <v>57594000</v>
+        <v>129248000</v>
       </c>
       <c r="BL5" t="n">
-        <v>268688000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>45000</v>
-      </c>
+        <v>299501000</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
-        <v>268688000</v>
+        <v>299501000</v>
       </c>
       <c r="BO5" t="n">
-        <v>18301000</v>
+        <v>151752000</v>
       </c>
       <c r="BP5" t="n">
-        <v>250387000</v>
+        <v>147749000</v>
       </c>
     </row>
   </sheetData>
@@ -2646,182 +2646,180 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>456548000</v>
+        <v>224003000</v>
       </c>
       <c r="C2" t="n">
-        <v>-108451000</v>
+        <v>-75576000</v>
       </c>
       <c r="D2" t="n">
-        <v>103186000</v>
+        <v>287000000</v>
       </c>
       <c r="E2" t="n">
-        <v>-106117000</v>
+        <v>-1487000</v>
       </c>
       <c r="F2" t="n">
-        <v>299501000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>268688000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-35410000</v>
+      </c>
       <c r="H2" t="n">
-        <v>275667000</v>
+        <v>78795000</v>
       </c>
       <c r="I2" t="n">
-        <v>-163000</v>
+        <v>868000</v>
       </c>
       <c r="J2" t="n">
-        <v>23997000</v>
+        <v>224435000</v>
       </c>
       <c r="K2" t="n">
-        <v>-499601000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>-35410000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>49493000</v>
+      </c>
       <c r="M2" t="n">
-        <v>-91164000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-77192000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-77192000</v>
-      </c>
+        <v>-58978000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-5265000</v>
+        <v>211424000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5265000</v>
+        <v>211424000</v>
       </c>
       <c r="R2" t="n">
-        <v>-108451000</v>
+        <v>-75576000</v>
       </c>
       <c r="S2" t="n">
-        <v>103186000</v>
+        <v>287000000</v>
       </c>
       <c r="T2" t="n">
-        <v>-39067000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
+        <v>-1055000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-905000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="n">
-        <v>-17613000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-17613000</v>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>-21454000</v>
+        <v>-150000</v>
       </c>
       <c r="AB2" t="n">
-        <v>84663000</v>
+        <v>1337000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-106117000</v>
+        <v>-1487000</v>
       </c>
       <c r="AD2" t="n">
-        <v>562665000</v>
+        <v>225490000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-12501000</v>
+        <v>-3761000</v>
       </c>
       <c r="AF2" t="n">
-        <v>28492000</v>
+        <v>-25816000</v>
       </c>
       <c r="AG2" t="n">
-        <v>47776000</v>
+        <v>14878000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3796000</v>
+        <v>-269000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-19053000</v>
+        <v>-40315000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>90957000</v>
+        <v>56180000</v>
       </c>
       <c r="AK2" t="n">
-        <v>323906000</v>
+        <v>222885000</v>
       </c>
       <c r="AL2" t="n">
-        <v>323906000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-16921000</v>
-      </c>
+        <v>222885000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>90815000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>75807000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2620000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>76619000</v>
+        <v>-141072000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>338607000</v>
+        <v>353520000</v>
       </c>
       <c r="C3" t="n">
-        <v>-57167000</v>
+        <v>-40495000</v>
       </c>
       <c r="D3" t="n">
-        <v>31319000</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-13000000</v>
+        <v>-6785000</v>
       </c>
       <c r="F3" t="n">
-        <v>275667000</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>293327000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-342893000</v>
+      </c>
       <c r="H3" t="n">
-        <v>293327000</v>
+        <v>268688000</v>
       </c>
       <c r="I3" t="n">
-        <v>-4691000</v>
+        <v>3243000</v>
       </c>
       <c r="J3" t="n">
-        <v>-12969000</v>
+        <v>21396000</v>
       </c>
       <c r="K3" t="n">
-        <v>-351796000</v>
+        <v>-349379000</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-69486000</v>
+        <v>-49997000</v>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>-25848000</v>
+        <v>-40495000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-25848000</v>
+        <v>-40495000</v>
       </c>
       <c r="R3" t="n">
-        <v>-57167000</v>
+        <v>-40495000</v>
       </c>
       <c r="S3" t="n">
-        <v>31319000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-12780000</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>10470000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-4053000</v>
+      </c>
       <c r="V3" t="n">
-        <v>1629000</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -2829,121 +2827,113 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>-13000000</v>
+        <v>14523000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>21308000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-13000000</v>
+        <v>-6785000</v>
       </c>
       <c r="AD3" t="n">
-        <v>351607000</v>
+        <v>360305000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-9191000</v>
+        <v>-68000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-51132000</v>
+        <v>-24524000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-944000</v>
+        <v>31096000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2230000</v>
+        <v>-335000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-48599000</v>
+        <v>-55539000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>68065000</v>
+        <v>46300000</v>
       </c>
       <c r="AK3" t="n">
-        <v>238991000</v>
+        <v>217063000</v>
       </c>
       <c r="AL3" t="n">
-        <v>238991000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>6909000</v>
-      </c>
+        <v>217063000</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>-134454000</v>
+        <v>95308000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>40894000</v>
       </c>
       <c r="AP3" t="n">
-        <v>240531000</v>
+        <v>77138000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>353520000</v>
+        <v>338607000</v>
       </c>
       <c r="C4" t="n">
-        <v>-40495000</v>
+        <v>-57167000</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>31319000</v>
       </c>
       <c r="E4" t="n">
-        <v>-6785000</v>
+        <v>-13000000</v>
       </c>
       <c r="F4" t="n">
+        <v>275667000</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>293327000</v>
       </c>
-      <c r="G4" t="n">
-        <v>-342893000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>268688000</v>
-      </c>
       <c r="I4" t="n">
-        <v>3243000</v>
+        <v>-4691000</v>
       </c>
       <c r="J4" t="n">
-        <v>21396000</v>
+        <v>-12969000</v>
       </c>
       <c r="K4" t="n">
-        <v>-349379000</v>
+        <v>-351796000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-49997000</v>
+        <v>-69486000</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>-40495000</v>
+        <v>-25848000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-40495000</v>
+        <v>-25848000</v>
       </c>
       <c r="R4" t="n">
-        <v>-40495000</v>
+        <v>-57167000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>31319000</v>
       </c>
       <c r="T4" t="n">
-        <v>10470000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-4053000</v>
-      </c>
+        <v>-12780000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1629000</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -2951,169 +2941,179 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
       <c r="AA4" t="n">
-        <v>14523000</v>
+        <v>-13000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>21308000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6785000</v>
+        <v>-13000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>360305000</v>
+        <v>351607000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-68000</v>
+        <v>-9191000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-24524000</v>
+        <v>-51132000</v>
       </c>
       <c r="AG4" t="n">
-        <v>31096000</v>
+        <v>-944000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-335000</v>
+        <v>-2230000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-55539000</v>
+        <v>-48599000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>46300000</v>
+        <v>68065000</v>
       </c>
       <c r="AK4" t="n">
-        <v>217063000</v>
+        <v>238991000</v>
       </c>
       <c r="AL4" t="n">
-        <v>217063000</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
+        <v>238991000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>6909000</v>
+      </c>
       <c r="AN4" t="n">
-        <v>95308000</v>
+        <v>-134454000</v>
       </c>
       <c r="AO4" t="n">
-        <v>40894000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>77138000</v>
+        <v>240531000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>224003000</v>
+        <v>456548000</v>
       </c>
       <c r="C5" t="n">
-        <v>-75576000</v>
+        <v>-108451000</v>
       </c>
       <c r="D5" t="n">
-        <v>287000000</v>
+        <v>103186000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1487000</v>
+        <v>-106117000</v>
       </c>
       <c r="F5" t="n">
-        <v>268688000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-35410000</v>
-      </c>
+        <v>299501000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>78795000</v>
+        <v>275667000</v>
       </c>
       <c r="I5" t="n">
-        <v>868000</v>
+        <v>-163000</v>
       </c>
       <c r="J5" t="n">
-        <v>224435000</v>
+        <v>23997000</v>
       </c>
       <c r="K5" t="n">
-        <v>-35410000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>49493000</v>
-      </c>
+        <v>-499601000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-58978000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>-91164000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-77192000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-77192000</v>
+      </c>
       <c r="P5" t="n">
-        <v>211424000</v>
+        <v>-5265000</v>
       </c>
       <c r="Q5" t="n">
-        <v>211424000</v>
+        <v>-5265000</v>
       </c>
       <c r="R5" t="n">
-        <v>-75576000</v>
+        <v>-108451000</v>
       </c>
       <c r="S5" t="n">
-        <v>287000000</v>
+        <v>103186000</v>
       </c>
       <c r="T5" t="n">
-        <v>-1055000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-905000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>-39067000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>-17613000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-17613000</v>
+      </c>
       <c r="AA5" t="n">
-        <v>-150000</v>
+        <v>-21454000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1337000</v>
+        <v>84663000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1487000</v>
+        <v>-106117000</v>
       </c>
       <c r="AD5" t="n">
-        <v>225490000</v>
+        <v>562665000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-3761000</v>
+        <v>-12501000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-25816000</v>
+        <v>28492000</v>
       </c>
       <c r="AG5" t="n">
-        <v>14878000</v>
+        <v>47776000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-269000</v>
+        <v>-3796000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-40315000</v>
+        <v>-19053000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>56180000</v>
+        <v>90957000</v>
       </c>
       <c r="AK5" t="n">
-        <v>222885000</v>
+        <v>323906000</v>
       </c>
       <c r="AL5" t="n">
-        <v>222885000</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+        <v>323906000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-16921000</v>
+      </c>
       <c r="AN5" t="n">
-        <v>75807000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>2620000</v>
-      </c>
+        <v>90815000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-141072000</v>
+        <v>76619000</v>
       </c>
     </row>
   </sheetData>
@@ -3588,182 +3588,182 @@
       </c>
       <c r="CN1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="DX1" t="inlineStr">
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3856,34 +3856,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="T2" t="n">
         <v>12.32</v>
       </c>
-      <c r="T2" t="n">
-        <v>12.2</v>
-      </c>
       <c r="U2" t="n">
-        <v>12.2</v>
+        <v>12.32</v>
       </c>
       <c r="V2" t="n">
-        <v>12.2</v>
+        <v>12.32</v>
       </c>
       <c r="W2" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="X2" t="n">
         <v>12.32</v>
       </c>
-      <c r="X2" t="n">
-        <v>12.2</v>
-      </c>
       <c r="Y2" t="n">
-        <v>12.2</v>
+        <v>12.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.2</v>
+        <v>12.32</v>
       </c>
       <c r="AA2" t="n">
         <v>0.59</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.73</v>
+        <v>4.79</v>
       </c>
       <c r="AC2" t="n">
         <v>1786579200</v>
@@ -3892,10 +3892,10 @@
         <v>0.262</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.708</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.5185184</v>
+        <v>4.5799255</v>
       </c>
       <c r="AG2" t="n">
         <v>3</v>
@@ -3913,10 +3913,10 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>12.24</v>
+        <v>12.2</v>
       </c>
       <c r="AM2" t="n">
-        <v>12.92</v>
+        <v>12.88</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
@@ -3925,10 +3925,10 @@
         <v>216</v>
       </c>
       <c r="AP2" t="n">
-        <v>214033744</v>
+        <v>216138992</v>
       </c>
       <c r="AQ2" t="n">
-        <v>219463326</v>
+        <v>222272797</v>
       </c>
       <c r="AR2" t="n">
         <v>11.42</v>
@@ -3943,10 +3943,10 @@
         <v>2.665</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.3492</v>
+        <v>12.3896</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.9825</v>
+        <v>12.9973</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.07541</v>
+        <v>0.01242</v>
       </c>
       <c r="BC2" t="n">
-        <v>8507666</v>
+        <v>9118540</v>
       </c>
       <c r="BD2" t="n">
         <v>17543750</v>
@@ -3984,7 +3984,7 @@
         <v>33.636</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.3627066</v>
+        <v>0.3662742</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -3993,16 +3993,16 @@
         <v>1798675200</v>
       </c>
       <c r="BL2" t="n">
-        <v>1767139200</v>
+        <v>1774915200</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0.11366904</v>
+        <v>-0.05972433</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BP2" t="n">
         <v>2.5</v>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>12.2</v>
+        <v>12.32</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -4024,34 +4024,34 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>570534976</v>
+        <v>568177984</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.592</v>
+        <v>0.508</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.673</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="BX2" t="n">
-        <v>414.12</v>
+        <v>682.793</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0322</v>
+        <v>0.02819</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.53723</v>
+        <v>0.10356</v>
       </c>
       <c r="CA2" t="n">
-        <v>351870112</v>
+        <v>372327872</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0.075</v>
+        <v>0.037</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.07732</v>
+        <v>0.06988</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.19326</v>
+        <v>0.19135</v>
       </c>
       <c r="CE2" t="n">
         <v>0</v>
@@ -4094,141 +4094,141 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CN2" t="n">
-        <v>2.7</v>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="CO2" t="n">
-        <v>-0.14920044</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>-0.01208179</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>-0.78250027</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>-0.060273465</v>
-      </c>
-      <c r="CS2" t="n">
+        <v>1782108751</v>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>finmb_145636942</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="CV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0.3257326</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>Enter Air S.A.</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>12.32 - 12.32</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.8999996</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.07880907500000001</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>11.42 - 15.42</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>-3.1000004</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.20103763</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-5.972433</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.069600105</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.005617623</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.6773004500000001</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.05211086</v>
+      </c>
+      <c r="DO2" t="n">
         <v>15</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="DP2" t="n">
         <v>15</v>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>Enter Air SA                  I</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
         <is>
           <t>Enter Air Sp. z o.o.</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="CW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="CY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.77999973</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>0.06830120000000001</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>11.42 - 15.42</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
-        <v>-3.2200003</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.20881973</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>-11.366903</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>-0.97402513</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>Enter Air SA                  I</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Enter Air S.A.</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1780380267</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>finmb_145636942</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
       </c>
       <c r="DT2" t="b">
         <v>0</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
         <v>1453791600000</v>
       </c>
-      <c r="DV2" t="n">
-        <v>-0.119999886</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>12.2 - 12.2</t>
-        </is>
+      <c r="DW2" t="n">
+        <v>0.03999996</v>
       </c>
       <c r="DX2" t="inlineStr"/>
     </row>
